--- a/results/link-prediction-gcn/Link/3shot/Wisconsin/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/3shot/Wisconsin/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.3542±0.0000</t>
+          <t>0.6389±0.0982</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.4792±0.0000</t>
+          <t>0.5347±0.0491</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>0.5139±0.0687</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.5903±0.0098</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0741</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0613</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.5347±0.0491</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.5694±0.0708</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5694±0.0708</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5694±0.0708</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.5417±0.0340</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.6042±0.0510</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.5972±0.0687</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.5833±0.0613</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.5833±0.0851</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.5833±0.0340</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5903±0.0428</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.5764±0.0354</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.5764±0.0196</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.5347±0.0354</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5833±0.0510</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5833±0.0510</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.5833±0.0510</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.6042±0.0613</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.6597±0.0491</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.5903±0.0098</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.4792±0.0000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0520</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0260</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0687</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0767</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.5694±0.0354</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5278±0.0196</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0393</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0520</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0393</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5833±0.0680</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.5903±0.0260</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.5208±0.0295</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.6736±0.0196</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5903±0.0393</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.5903±0.0520</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5972±0.0520</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.6319±0.0708</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.6250±0.0450</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.6111±0.0597</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.6181±0.0937</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.6181±0.0937</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.6181±0.0937</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.6181±0.0354</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.6042±0.0900</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.6528±0.0428</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0786</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0354</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0098</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.5417±0.0680</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.5347±0.0354</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.5694±0.0520</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0354</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0354</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0354</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0354</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.6111±0.0804</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.6458±0.0340</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.5278±0.0393</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>0.6111±0.0804</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.3958±0.0000</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.4792±0.0000</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.4792±0.0000</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0.6458±0.0000</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.4583±0.0000</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.7083±0.0000</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.5833±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.6458±0.0000</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.4792±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.4792±0.0000</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.4792±0.0000</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5347±0.0260</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5556±0.0098</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5208±0.0170</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5486±0.0354</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5625±0.0000</t>
+          <t>0.5556±0.0196</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5208±0.0170</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5208±0.0170</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5208±0.0170</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.6458±0.0000</t>
+          <t>0.5764±0.0520</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5972±0.0491</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.5139±0.0196</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5417±0.0589</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5347±0.0687</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.4375±0.0000</t>
+          <t>0.6042±0.0170</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5208±0.0170</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5278±0.0098</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5278±0.0393</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.5347±0.0260</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6250±0.0613</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6250±0.0613</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6250±0.0613</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.6319±0.0708</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5625±0.0000</t>
+          <t>0.6250±0.0450</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.6528±0.0196</t>
         </is>
       </c>
     </row>
@@ -1355,457 +1355,457 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.3673±0.0000</t>
+          <t>0.6889±0.0437</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.6154±0.0000</t>
+          <t>0.6626±0.0057</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>0.6450±0.0592</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.6763±0.0173</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.6920±0.0295</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.6969±0.0304</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.6833±0.0235</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.6922±0.0294</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6922±0.0294</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6922±0.0294</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.6830±0.0167</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.6918±0.0203</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.7023±0.0293</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.2906±0.2094</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.6410±0.1095</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6807±0.0100</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6706±0.0264</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.7029±0.0177</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.6963±0.0161</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.6577±0.0391</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6854±0.0226</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6854±0.0226</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6854±0.0226</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.6822±0.0639</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.7269±0.0302</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.7004±0.0039</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.5763±0.0000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.5999±0.0842</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6571±0.0077</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6783±0.0314</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.6815±0.0416</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.6935±0.0127</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6794±0.0090</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.6550±0.0556</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.6932±0.0253</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.6550±0.0556</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.6848±0.0404</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.6897±0.0295</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.6763±0.0137</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.5649±0.0573</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6591±0.0306</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6498±0.0719</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6752±0.0276</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.6999±0.0610</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.6966±0.0540</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.6807±0.0526</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.6862±0.0587</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.6862±0.0587</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.6862±0.0587</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.6769±0.0402</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.6538±0.0559</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7085±0.0384</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.6444±0.0314</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6473±0.0714</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6478±0.0144</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6246±0.0558</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6797±0.0185</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6733±0.0094</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6927±0.0172</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6927±0.0172</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6927±0.0172</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.7042±0.0344</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7138±0.0340</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.6696±0.0285</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.6600±0.0190</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>0.6111±0.0786</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6601±0.0092</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6686±0.0261</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.6957±0.0000</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.6761±0.0000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.6761±0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.6761±0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.5714±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.3256±0.0000</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.6269±0.0000</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.7188±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.7164±0.0000</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0.6479±0.0000</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.7273±0.0000</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.7273±0.0000</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.7273±0.0000</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.6857±0.0000</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.7241±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.7119±0.0000</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.5667±0.0000</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.6761±0.0000</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.6857±0.0000</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.7667±0.0000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.6761±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.6761±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.6761±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0.6866±0.0000</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.6857±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.6857±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6562±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6774±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.7213±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.6562±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.7188±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.6885±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.6885±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.6885±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.7333±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.6885±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.7241±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6154±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6984±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6479±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6761±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.6769±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.6479±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6571±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6864±0.0140</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.6769±0.0000</t>
+          <t>0.6352±0.0447</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6596±0.0203</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6596±0.0203</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6596±0.0203</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.7385±0.0000</t>
+          <t>0.6553±0.0759</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6470±0.0611</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.7059±0.0000</t>
+          <t>0.6633±0.0164</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6349±0.0449</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.6648±0.0262</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.5970±0.0000</t>
+          <t>0.6952±0.0134</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6133±0.0169</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6631±0.0126</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6597±0.0050</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.7164±0.0000</t>
+          <t>0.6731±0.0200</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.7053±0.0251</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.7053±0.0251</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.7053±0.0251</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6452±0.0000</t>
+          <t>0.7131±0.0320</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6866±0.0000</t>
+          <t>0.6918±0.0443</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.7369±0.0132</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.3125±0.0000</t>
+          <t>0.7604±0.0317</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.7193±0.0209</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.6753±0.0000</t>
+          <t>0.7023±0.0793</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.5408±0.0000</t>
+          <t>0.6678±0.0622</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.6719±0.0000</t>
+          <t>0.7332±0.0532</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.7196±0.0000</t>
+          <t>0.7332±0.0394</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.7552±0.0000</t>
+          <t>0.7124±0.0356</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.8212±0.0000</t>
+          <t>0.7561±0.0193</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8212±0.0000</t>
+          <t>0.7561±0.0193</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.8212±0.0000</t>
+          <t>0.7561±0.0193</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.8125±0.0000</t>
+          <t>0.7749±0.0722</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.5625±0.0000</t>
+          <t>0.6887±0.0421</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.6493±0.0000</t>
+          <t>0.7072±0.0908</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.3924±0.0000</t>
+          <t>0.7483±0.0375</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.6128±0.0000</t>
+          <t>0.6979±0.1339</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.5599±0.0000</t>
+          <t>0.6565±0.0721</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.7031±0.0000</t>
+          <t>0.6730±0.0411</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.6970±0.0000</t>
+          <t>0.6808±0.0662</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.6241±0.0000</t>
+          <t>0.7413±0.0357</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.7448±0.0000</t>
+          <t>0.6985±0.0872</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.7413±0.0000</t>
+          <t>0.7095±0.0172</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7413±0.0000</t>
+          <t>0.7095±0.0172</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.7413±0.0000</t>
+          <t>0.7095±0.0172</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.8073±0.0000</t>
+          <t>0.6696±0.1373</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7951±0.0000</t>
+          <t>0.7454±0.0578</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7552±0.0000</t>
+          <t>0.7535±0.0197</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.3733±0.0000</t>
+          <t>0.7737±0.0090</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.5816±0.0000</t>
+          <t>0.6383±0.0936</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.6528±0.0000</t>
+          <t>0.7274±0.0418</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.7752±0.0000</t>
+          <t>0.7422±0.0588</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.7413±0.0000</t>
+          <t>0.6655±0.0985</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.7865±0.0000</t>
+          <t>0.7737±0.0554</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.8646±0.0000</t>
+          <t>0.7274±0.0867</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.7969±0.0000</t>
+          <t>0.7821±0.0900</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.7969±0.0000</t>
+          <t>0.7002±0.0842</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.7969±0.0000</t>
+          <t>0.7821±0.0900</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.8247±0.0000</t>
+          <t>0.7257±0.0937</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.7448±0.0000</t>
+          <t>0.7749±0.0850</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.7604±0.0000</t>
+          <t>0.7468±0.0338</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.6406±0.0000</t>
+          <t>0.6209±0.0565</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.7726±0.0000</t>
+          <t>0.6244±0.1162</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.5391±0.0000</t>
+          <t>0.5984±0.0413</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.6016±0.0000</t>
+          <t>0.5958±0.0487</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.6510±0.0000</t>
+          <t>0.6788±0.0920</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.5365±0.0000</t>
+          <t>0.6994±0.0787</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.7500±0.0000</t>
+          <t>0.6910±0.0288</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.6181±0.0937</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.6181±0.0937</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.6181±0.0937</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.6701±0.0000</t>
+          <t>0.6999±0.0808</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.7222±0.0000</t>
+          <t>0.6632±0.0887</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.6797±0.0000</t>
+          <t>0.6606±0.0434</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.4358±0.0000</t>
+          <t>0.7760±0.0014</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.6389±0.0000</t>
+          <t>0.7043±0.1273</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.6415±0.0000</t>
+          <t>0.6606±0.0421</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.6597±0.0000</t>
+          <t>0.6189±0.1010</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.6910±0.0000</t>
+          <t>0.7387±0.0117</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.8116±0.0000</t>
+          <t>0.7141±0.0464</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.8212±0.0000</t>
+          <t>0.7558±0.1019</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.7812±0.0000</t>
+          <t>0.7807±0.0290</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.7812±0.0000</t>
+          <t>0.7807±0.0290</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.7812±0.0000</t>
+          <t>0.7807±0.0290</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.8507±0.0000</t>
+          <t>0.7546±0.0298</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.7812±0.0000</t>
+          <t>0.7899±0.0772</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.7951±0.0000</t>
+          <t>0.7373±0.0834</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.3229±0.0000</t>
+          <t>0.7668±0.0030</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.7483±0.0000</t>
+          <t>0.6748±0.0759</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.6684±0.0000</t>
+          <t>0.6956±0.0534</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.6892±0.0000</t>
+          <t>0.6690±0.0557</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.7257±0.0000</t>
+          <t>0.7286±0.0857</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.7535±0.0000</t>
+          <t>0.7370±0.0896</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.6701±0.0000</t>
+          <t>0.6435±0.0537</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.7431±0.0000</t>
+          <t>0.7274±0.0149</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.7431±0.0000</t>
+          <t>0.7274±0.0149</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.7431±0.0000</t>
+          <t>0.7274±0.0149</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.8767±0.0000</t>
+          <t>0.7610±0.1467</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6510±0.0000</t>
+          <t>0.6655±0.1024</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.7951±0.0000</t>
+          <t>0.7124±0.0291</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.3872±0.0000</t>
+          <t>0.7159±0.0629</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.6910±0.0000</t>
+          <t>0.7222±0.0686</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.5104±0.0000</t>
+          <t>0.6707±0.0838</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.6024±0.0000</t>
+          <t>0.6198±0.0347</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.5521±0.0000</t>
+          <t>0.6944±0.0883</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5677±0.0000</t>
+          <t>0.6968±0.0161</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.7188±0.0000</t>
+          <t>0.7581±0.0879</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.6163±0.0000</t>
+          <t>0.7341±0.0210</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.6163±0.0000</t>
+          <t>0.7341±0.0210</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.6163±0.0000</t>
+          <t>0.7341±0.0210</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.6562±0.0000</t>
+          <t>0.7922±0.0454</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.7118±0.1002</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.7274±0.0000</t>
+          <t>0.7975±0.0576</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.4216±0.0000</t>
+          <t>0.8048±0.0142</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6296±0.0000</t>
+          <t>0.7802±0.0317</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.6071±0.0000</t>
+          <t>0.7446±0.0469</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5716±0.0000</t>
+          <t>0.6584±0.0661</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.6350±0.0000</t>
+          <t>0.7526±0.0543</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.7036±0.0000</t>
+          <t>0.7309±0.0585</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.8243±0.0000</t>
+          <t>0.7346±0.0840</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.8377±0.0000</t>
+          <t>0.7602±0.0345</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8377±0.0000</t>
+          <t>0.7602±0.0345</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.8377±0.0000</t>
+          <t>0.7602±0.0345</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.8558±0.0000</t>
+          <t>0.8155±0.0628</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.5954±0.0000</t>
+          <t>0.6874±0.0282</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.6051±0.0000</t>
+          <t>0.6680±0.1127</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.4745±0.0000</t>
+          <t>0.7541±0.0079</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7034±0.0000</t>
+          <t>0.7515±0.1080</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5383±0.0000</t>
+          <t>0.6511±0.1096</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.6491±0.0000</t>
+          <t>0.6980±0.0703</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.6309±0.0000</t>
+          <t>0.6198±0.0587</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.5919±0.0000</t>
+          <t>0.7013±0.0590</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7834±0.0000</t>
+          <t>0.7590±0.0712</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.6767±0.0000</t>
+          <t>0.6853±0.0418</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6767±0.0000</t>
+          <t>0.6853±0.0418</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.6767±0.0000</t>
+          <t>0.6853±0.0418</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7951±0.0000</t>
+          <t>0.6825±0.0976</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.8147±0.0000</t>
+          <t>0.7544±0.0436</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7332±0.0000</t>
+          <t>0.6983±0.0437</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.4962±0.0000</t>
+          <t>0.7806±0.0404</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.7016±0.0000</t>
+          <t>0.6903±0.0657</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6350±0.0000</t>
+          <t>0.7095±0.0591</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.7808±0.0000</t>
+          <t>0.7159±0.0895</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.7941±0.0000</t>
+          <t>0.6757±0.0846</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.8288±0.0000</t>
+          <t>0.7825±0.0725</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.8418±0.0000</t>
+          <t>0.7570±0.0671</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.7879±0.0000</t>
+          <t>0.8041±0.0729</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.7879±0.0000</t>
+          <t>0.7060±0.0825</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.7879±0.0000</t>
+          <t>0.8041±0.0729</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.8437±0.0000</t>
+          <t>0.7405±0.0775</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.7793±0.0000</t>
+          <t>0.8000±0.0798</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.7641±0.0000</t>
+          <t>0.7066±0.0569</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.6707±0.0000</t>
+          <t>0.7061±0.0547</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.8201±0.0000</t>
+          <t>0.6836±0.1459</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.5219±0.0000</t>
+          <t>0.5589±0.0235</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5591±0.0000</t>
+          <t>0.5583±0.0343</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.5905±0.0000</t>
+          <t>0.6210±0.0607</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.5219±0.0000</t>
+          <t>0.6627±0.0765</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.7121±0.0000</t>
+          <t>0.6676±0.0286</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.5591±0.0000</t>
+          <t>0.5781±0.0712</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.5591±0.0000</t>
+          <t>0.5781±0.0712</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.5591±0.0000</t>
+          <t>0.5781±0.0712</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.6144±0.0000</t>
+          <t>0.7061±0.1123</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.7201±0.0000</t>
+          <t>0.7120±0.0838</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.6193±0.0000</t>
+          <t>0.6010±0.0352</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.5374±0.0000</t>
+          <t>0.8153±0.0154</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.7310±0.0000</t>
+          <t>0.7535±0.1120</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.6147±0.0000</t>
+          <t>0.6443±0.0597</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.6916±0.0000</t>
+          <t>0.6485±0.0979</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.7583±0.0000</t>
+          <t>0.7202±0.0146</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.7873±0.0000</t>
+          <t>0.7301±0.0593</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.8511±0.0000</t>
+          <t>0.7658±0.1130</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.8178±0.0000</t>
+          <t>0.8008±0.0409</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.8178±0.0000</t>
+          <t>0.8008±0.0409</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.8178±0.0000</t>
+          <t>0.8008±0.0409</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.8826±0.0000</t>
+          <t>0.7385±0.0536</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.8286±0.0000</t>
+          <t>0.8184±0.0502</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.8308±0.0000</t>
+          <t>0.7574±0.0832</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.4708±0.0000</t>
+          <t>0.8094±0.0082</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.7997±0.0000</t>
+          <t>0.7320±0.1006</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.6129±0.0000</t>
+          <t>0.7070±0.0487</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.6129±0.0000</t>
+          <t>0.6594±0.0330</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7998±0.0000</t>
+          <t>0.7361±0.0973</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.8144±0.0000</t>
+          <t>0.7470±0.0969</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.7390±0.0000</t>
+          <t>0.7020±0.0355</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.7758±0.0000</t>
+          <t>0.7679±0.0272</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.7758±0.0000</t>
+          <t>0.7679±0.0272</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.7758±0.0000</t>
+          <t>0.7679±0.0272</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.8668±0.0000</t>
+          <t>0.7995±0.1219</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7284±0.0000</t>
+          <t>0.7035±0.0978</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.7864±0.0000</t>
+          <t>0.7233±0.0493</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.5285±0.0000</t>
+          <t>0.7625±0.0570</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.7305±0.0000</t>
+          <t>0.7557±0.0778</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.5196±0.0000</t>
+          <t>0.6525±0.1192</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.6823±0.0000</t>
+          <t>0.6587±0.0234</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6099±0.0000</t>
+          <t>0.6945±0.0899</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.6611±0.0000</t>
+          <t>0.7570±0.0055</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.7338±0.0000</t>
+          <t>0.8047±0.0780</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7428±0.0000</t>
+          <t>0.7129±0.0495</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7428±0.0000</t>
+          <t>0.7129±0.0495</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7428±0.0000</t>
+          <t>0.7129±0.0495</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.7382±0.0000</t>
+          <t>0.8043±0.0512</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.6976±0.0000</t>
+          <t>0.7336±0.0919</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.8189±0.0613</t>
         </is>
       </c>
     </row>
